--- a/media/exports/reports/2026-01/people-helped.xlsx
+++ b/media/exports/reports/2026-01/people-helped.xlsx
@@ -16,7 +16,7 @@
     <definedName name="People_helped_January">'Report'!$B$8</definedName>
     <definedName name="Couldn_t_reach_January">'Report'!$B$9</definedName>
     <definedName name="Share_reached_January">'Report'!$B$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$E$21</definedName>
@@ -301,20 +301,6 @@
             </spPr>
           </dPt>
           <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
             <idx val="2"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -442,7 +428,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1.0603"/>
+          <max val="1.05685"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -456,7 +442,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1.0603"/>
+          <max val="1.05685"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -816,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -842,7 +828,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -900,7 +886,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>December 55</t>
+          <t>December 43</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1030,7 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1056,90 +1042,78 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Couldn't make contact</t>
+          <t>Not eligible</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Not eligible</t>
+          <t>Couldn't make contact</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Outside the service area</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>427 people were helped in January, and 69 came to a program but couldn't be helped: 86.1% reached (target 90.0%), against 90.5% in December.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>427 people were helped in January, and 49 came to a program but couldn't be helped: 89.7% reached (target 90.0%), against 92.4% in December.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Community meals reached the smallest share: 84.0% (32 couldn't be helped). The main reason: program at capacity (26 people).</t>
-        </is>
-      </c>
-    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Community meals reached the smallest share: 88.4% (22 couldn't be helped). The main reason: program at capacity (20 people).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1184,7 +1158,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1236,10 +1210,10 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -1306,10 +1280,10 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -1376,10 +1350,10 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -1438,7 +1412,7 @@
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -1493,7 +1467,7 @@
         </is>
       </c>
       <c r="B41" s="15" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -1548,7 +1522,7 @@
         </is>
       </c>
       <c r="B49" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50">
@@ -1603,7 +1577,7 @@
         </is>
       </c>
       <c r="B57" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -1626,7 +1600,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1717,7 +1691,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1738,7 @@
         <v>175</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6" s="19">
         <f>IF(C6+D6=0,"",C6/(C6+D6))</f>
@@ -1786,7 +1760,7 @@
         <v>211</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" s="19">
         <f>IF(C7+D7=0,"",C7/(C7+D7))</f>
@@ -1808,7 +1782,7 @@
         <v>195</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E8" s="19">
         <f>IF(C8+D8=0,"",C8/(C8+D8))</f>
@@ -1852,7 +1826,7 @@
         <v>297</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E10" s="19">
         <f>IF(C10+D10=0,"",C10/(C10+D10))</f>
@@ -1874,7 +1848,7 @@
         <v>278</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E11" s="19">
         <f>IF(C11+D11=0,"",C11/(C11+D11))</f>
@@ -1896,7 +1870,7 @@
         <v>314</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E12" s="19">
         <f>IF(C12+D12=0,"",C12/(C12+D12))</f>
@@ -1918,7 +1892,7 @@
         <v>305</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E13" s="19">
         <f>IF(C13+D13=0,"",C13/(C13+D13))</f>
@@ -1940,7 +1914,7 @@
         <v>265</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E14" s="19">
         <f>IF(C14+D14=0,"",C14/(C14+D14))</f>
@@ -1962,7 +1936,7 @@
         <v>425</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E15" s="19">
         <f>IF(C15+D15=0,"",C15/(C15+D15))</f>
@@ -1984,7 +1958,7 @@
         <v>446</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E16" s="19">
         <f>IF(C16+D16=0,"",C16/(C16+D16))</f>
@@ -2006,7 +1980,7 @@
         <v>474</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E17" s="19">
         <f>IF(C17+D17=0,"",C17/(C17+D17))</f>
@@ -2028,7 +2002,7 @@
         <v>506</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E18" s="19">
         <f>IF(C18+D18=0,"",C18/(C18+D18))</f>
@@ -2050,7 +2024,7 @@
         <v>495</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19" s="19">
         <f>IF(C19+D19=0,"",C19/(C19+D19))</f>
@@ -2072,7 +2046,7 @@
         <v>521</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E20" s="19">
         <f>IF(C20+D20=0,"",C20/(C20+D20))</f>
@@ -2094,7 +2068,7 @@
         <v>427</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E21" s="19">
         <f>IF(C21+D21=0,"",C21/(C21+D21))</f>
@@ -2107,7 +2081,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-01/people-helped.xlsx
+++ b/media/exports/reports/2026-01/people-helped.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="People_helped_January">'Report'!$B$8</definedName>
-    <definedName name="Couldn_t_reach_January">'Report'!$B$9</definedName>
-    <definedName name="Share_reached_January">'Report'!$B$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$39</definedName>
+    <definedName name="People_helped_January">'Report'!$B$9</definedName>
+    <definedName name="Couldn_t_reach_January">'Report'!$B$10</definedName>
+    <definedName name="Share_reached_January">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$E$21</definedName>
@@ -55,6 +55,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -75,11 +80,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -117,26 +117,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -144,12 +147,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -324,12 +327,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$14:$A$17</f>
+              <f>'Report'!$A$15:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$14:$B$17</f>
+              <f>'Report'!$B$15:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -478,7 +481,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -802,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -828,7 +831,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -836,158 +839,164 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: 427 people helped in January; 49 couldn't be reached (89.7% reached, target 90.0%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>People helped by each program, day by day, and the people who came to a program but couldn't be helped (and why). People helped are counted against each program's own grant spend.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>People helped, January</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>December 521</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Couldn't reach, January</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Workings!B18</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>December 43</t>
+          <t>People helped, January</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>December 521</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Couldn't reach, January</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>Workings!B17</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>December 43</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Share reached, January</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="9">
         <f>Workings!B26</f>
         <v/>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>target 90.0%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Share of people reached, by program, January 2026</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Share reached %</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>People helped</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Community meals</t>
-        </is>
-      </c>
-      <c r="B14" s="6">
-        <f>Workings!B34</f>
-        <v/>
-      </c>
-      <c r="C14" s="9">
-        <f>Workings!B33</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Youth outreach</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <f>Workings!B42</f>
-        <v/>
-      </c>
-      <c r="C15" s="9">
-        <f>Workings!B41</f>
+          <t>Community meals</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>Workings!B34</f>
+        <v/>
+      </c>
+      <c r="C15" s="7">
+        <f>Workings!B32</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Housing support</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>Workings!B50</f>
-        <v/>
-      </c>
-      <c r="C16" s="9">
-        <f>Workings!B49</f>
+          <t>Youth outreach</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>Workings!B42</f>
+        <v/>
+      </c>
+      <c r="C16" s="7">
+        <f>Workings!B40</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Housing support</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>Workings!B50</f>
+        <v/>
+      </c>
+      <c r="C17" s="7">
+        <f>Workings!B48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B18" s="9">
         <f>Workings!B58</f>
         <v/>
       </c>
-      <c r="C17" s="9">
-        <f>Workings!B57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="C18" s="7">
+        <f>Workings!B56</f>
+        <v/>
+      </c>
+    </row>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
@@ -995,132 +1004,134 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>People helped by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Why people couldn't be helped, January 2026</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Main reason</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Program at capacity</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Waitlist</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Not eligible</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Couldn't make contact</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>427 people were helped in January, and 49 came to a program but couldn't be helped: 89.7% reached (target 90.0%), against 92.4% in December.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Community meals reached the smallest share: 88.4% (22 couldn't be helped). The main reason: program at capacity (20 people).</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41"/>
+    <row r="42"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="27" min="0" max="16383" man="1"/>
+    <brk id="28" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1158,33 +1169,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>People helped, January and December</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -1196,10 +1207,10 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>427</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>521</v>
       </c>
     </row>
@@ -1209,24 +1220,24 @@
           <t>People we couldn't reach</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <f>B8/(B8+B9)</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <f>C8/(C8+C9)</f>
         <v/>
       </c>
@@ -1234,27 +1245,27 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>People helped, January and December</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -1266,10 +1277,10 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="16" t="n">
         <v>427</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>521</v>
       </c>
     </row>
@@ -1279,24 +1290,24 @@
           <t>People we couldn't reach</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="18">
         <f>B16/(B16+B17)</f>
         <v/>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="18">
         <f>C16/(C16+C17)</f>
         <v/>
       </c>
@@ -1304,27 +1315,27 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>People helped, January and December</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
@@ -1336,10 +1347,10 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B24" s="16" t="n">
         <v>427</v>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="16" t="n">
         <v>521</v>
       </c>
     </row>
@@ -1349,24 +1360,24 @@
           <t>People we couldn't reach</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n">
+      <c r="B25" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="16" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="18">
         <f>B24/(B24+B25)</f>
         <v/>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="18">
         <f>C24/(C24+C25)</f>
         <v/>
       </c>
@@ -1374,22 +1385,22 @@
     <row r="27"/>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Community meals, January 2026</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -1401,7 +1412,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
+      <c r="B32" s="16" t="n">
         <v>168</v>
       </c>
     </row>
@@ -1411,17 +1422,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
+      <c r="B33" s="16" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="18">
         <f>B32/(B32+B33)</f>
         <v/>
       </c>
@@ -1429,22 +1440,22 @@
     <row r="35"/>
     <row r="36"/>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Youth outreach, January 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -1456,7 +1467,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B40" s="16" t="n">
         <v>114</v>
       </c>
     </row>
@@ -1466,17 +1477,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="16" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="18">
         <f>B40/(B40+B41)</f>
         <v/>
       </c>
@@ -1484,22 +1495,22 @@
     <row r="43"/>
     <row r="44"/>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Housing support, January 2026</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -1511,7 +1522,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B48" s="15" t="n">
+      <c r="B48" s="16" t="n">
         <v>98</v>
       </c>
     </row>
@@ -1521,17 +1532,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B49" s="15" t="n">
+      <c r="B49" s="16" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="18">
         <f>B48/(B48+B49)</f>
         <v/>
       </c>
@@ -1539,22 +1550,22 @@
     <row r="51"/>
     <row r="52"/>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Digital literacy, January 2026</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr"/>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr"/>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -1566,7 +1577,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B56" s="15" t="n">
+      <c r="B56" s="16" t="n">
         <v>47</v>
       </c>
     </row>
@@ -1576,17 +1587,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B57" s="15" t="n">
+      <c r="B57" s="16" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="18">
         <f>B56/(B56+B57)</f>
         <v/>
       </c>
@@ -1600,7 +1611,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1691,386 +1702,386 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>People helped</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>175</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>IF(C6+D6=0,"",C6/(C6+D6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>211</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <f>IF(C7+D7=0,"",C7/(C7+D7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>195</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>IF(C8+D8=0,"",C8/(C8+D8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>308</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <f>IF(C9+D9=0,"",C9/(C9+D9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>297</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>IF(C10+D10=0,"",C10/(C10+D10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>278</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>IF(C11+D11=0,"",C11/(C11+D11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>314</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>IF(C12+D12=0,"",C12/(C12+D12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>305</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>IF(C13+D13=0,"",C13/(C13+D13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>265</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>IF(C14+D14=0,"",C14/(C14+D14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>425</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>68</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <f>IF(C15+D15=0,"",C15/(C15+D15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>446</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>65</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>IF(C16+D16=0,"",C16/(C16+D16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>474</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <f>IF(C17+D17=0,"",C17/(C17+D17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="16" t="n">
         <v>506</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <f>IF(C18+D18=0,"",C18/(C18+D18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="16" t="n">
         <v>495</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>52</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <f>IF(C19+D19=0,"",C19/(C19+D19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="16" t="n">
         <v>521</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>43</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <f>IF(C20+D20=0,"",C20/(C20+D20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <v>427</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <f>IF(C21+D21=0,"",C21/(C21+D21))</f>
         <v/>
       </c>
@@ -2081,7 +2092,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
